--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.9305848032940097</v>
+        <v>1.144548022837112</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-0.06941519670599772</v>
+        <v>0.1445480228371196</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-0.01353864585292919</v>
+        <v>0.02591080456492878</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.00334967184381707</v>
+        <v>0.04347450082447035</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.3093683704922247</v>
+        <v>0.2129774551083961</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.06257629125054212</v>
+        <v>0.1564244809473329</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.08980589154597358</v>
+        <v>0.2276654641481523</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.5809130893679793</v>
+        <v>0.4029157051285895</v>
       </c>
     </row>
     <row r="14">
@@ -699,7 +699,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年06月</t>
+          <t>2021年09月-2024年09月</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.0233058027107961</v>
+        <v>0.06430825166435102</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2600001846287696</v>
+        <v>0.166681808833382</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.126580863026736</v>
+        <v>0.2811753166025268</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.448802409309112</v>
+        <v>0.2060651325343261</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年06月</t>
+          <t>2022年10月-2026年04月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>23.80616828460282</v>
+        <v>17.78649872689564</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.09496875732918736</v>
+        <v>0.07095479041971464</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.2229976603211159</v>
+        <v>0.1718152768479839</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>2.168421052631579</v>
+        <v>7.653383458646617</v>
       </c>
     </row>
     <row r="24">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.144548022837112</v>
+        <v>0.7903399775427442</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.1445480228371196</v>
+        <v>-0.2096600224572615</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.02591080456492878</v>
+        <v>-0.04360249895069757</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.04347450082447035</v>
+        <v>-0.02722887744571645</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2129774551083961</v>
+        <v>0.22248100383439</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1564244809473329</v>
+        <v>-0.1561246495409726</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2276654641481523</v>
+        <v>-0.2197405527490282</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.4029157051285895</v>
+        <v>0.5037722864721367</v>
       </c>
     </row>
     <row r="14">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.06430825166435102</v>
+        <v>-0.08655200002374325</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.166681808833382</v>
+        <v>0.1937203030942629</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2811753166025268</v>
+        <v>-0.1093475795413515</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.2060651325343261</v>
+        <v>0.3955466236337561</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2022年10月-2026年04月</t>
+          <t>2021年09月-2025年10月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>17.78649872689564</v>
+        <v>18.30229045511369</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.07095479041971464</v>
+        <v>0.07301241258233816</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.1718152768479839</v>
+        <v>0.1765063918366495</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>7.653383458646617</v>
+        <v>2.842857142857143</v>
       </c>
     </row>
     <row r="24">
